--- a/AllYearsMerged.xlsx
+++ b/AllYearsMerged.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="434">
   <si>
     <t>CVR</t>
   </si>
@@ -1024,6 +1024,24 @@
     <t>10658446</t>
   </si>
   <si>
+    <t>27485111</t>
+  </si>
+  <si>
+    <t>34230625</t>
+  </si>
+  <si>
+    <t>56759913</t>
+  </si>
+  <si>
+    <t>15603712</t>
+  </si>
+  <si>
+    <t>38235311</t>
+  </si>
+  <si>
+    <t>31943329</t>
+  </si>
+  <si>
     <t>Visma Expense</t>
   </si>
   <si>
@@ -1295,6 +1313,9 @@
   </si>
   <si>
     <t>2024Q3</t>
+  </si>
+  <si>
+    <t>2024Q4</t>
   </si>
 </sst>
 </file>
@@ -1656,7 +1677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H360"/>
+  <dimension ref="A1:H367"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1696,16 +1717,16 @@
         <v>78556.39999999999</v>
       </c>
       <c r="D2" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="E2" s="2">
         <v>44200</v>
       </c>
       <c r="F2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H2" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1719,16 +1740,16 @@
         <v>30513.26</v>
       </c>
       <c r="D3" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E3" s="2">
         <v>44216</v>
       </c>
       <c r="F3" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H3" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1742,19 +1763,19 @@
         <v>77346.97</v>
       </c>
       <c r="D4" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E4" s="2">
         <v>44208</v>
       </c>
       <c r="F4" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G4" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H4" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1768,16 +1789,16 @@
         <v>52126.72</v>
       </c>
       <c r="D5" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E5" s="2">
         <v>44209</v>
       </c>
       <c r="F5" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H5" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1791,16 +1812,16 @@
         <v>13053.78</v>
       </c>
       <c r="D6" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E6" s="2">
         <v>44224</v>
       </c>
       <c r="F6" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="H6" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1814,16 +1835,16 @@
         <v>28895.99</v>
       </c>
       <c r="D7" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E7" s="2">
         <v>44202</v>
       </c>
       <c r="F7" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H7" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1837,16 +1858,16 @@
         <v>36113.01</v>
       </c>
       <c r="D8" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E8" s="2">
         <v>44218</v>
       </c>
       <c r="F8" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="H8" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1860,19 +1881,19 @@
         <v>50524.99</v>
       </c>
       <c r="D9" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E9" s="2">
         <v>44217</v>
       </c>
       <c r="F9" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G9" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="H9" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1886,19 +1907,19 @@
         <v>39790.38</v>
       </c>
       <c r="D10" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E10" s="2">
         <v>44228</v>
       </c>
       <c r="F10" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="G10" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H10" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1912,19 +1933,19 @@
         <v>59748.16</v>
       </c>
       <c r="D11" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E11" s="2">
         <v>44229</v>
       </c>
       <c r="F11" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="G11" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H11" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1938,19 +1959,19 @@
         <v>33865</v>
       </c>
       <c r="D12" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E12" s="2">
         <v>44235</v>
       </c>
       <c r="F12" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="G12" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="H12" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1964,19 +1985,19 @@
         <v>33865</v>
       </c>
       <c r="D13" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E13" s="2">
         <v>44235</v>
       </c>
       <c r="F13" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="G13" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="H13" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1990,19 +2011,19 @@
         <v>34478</v>
       </c>
       <c r="D14" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E14" s="2">
         <v>44235</v>
       </c>
       <c r="F14" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="G14" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="H14" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2016,19 +2037,19 @@
         <v>35072.02</v>
       </c>
       <c r="D15" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E15" s="2">
         <v>44235</v>
       </c>
       <c r="F15" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="G15" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="H15" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2042,19 +2063,19 @@
         <v>38161</v>
       </c>
       <c r="D16" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E16" s="2">
         <v>44235</v>
       </c>
       <c r="F16" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="G16" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="H16" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2068,19 +2089,19 @@
         <v>56812.75</v>
       </c>
       <c r="D17" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E17" s="2">
         <v>44235</v>
       </c>
       <c r="F17" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="G17" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="H17" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2094,16 +2115,16 @@
         <v>36304</v>
       </c>
       <c r="D18" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E18" s="2">
         <v>44243</v>
       </c>
       <c r="F18" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="H18" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2117,19 +2138,19 @@
         <v>20969.32</v>
       </c>
       <c r="D19" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E19" s="2">
         <v>44267</v>
       </c>
       <c r="F19" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="G19" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H19" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2143,16 +2164,16 @@
         <v>26744.54</v>
       </c>
       <c r="D20" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E20" s="2">
         <v>44260</v>
       </c>
       <c r="F20" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H20" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2166,16 +2187,16 @@
         <v>159260.11</v>
       </c>
       <c r="D21" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E21" s="2">
         <v>44265</v>
       </c>
       <c r="F21" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="H21" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -2189,16 +2210,16 @@
         <v>15000</v>
       </c>
       <c r="D22" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E22" s="2">
         <v>44267</v>
       </c>
       <c r="F22" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H22" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -2212,19 +2233,19 @@
         <v>33517.9</v>
       </c>
       <c r="D23" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E23" s="2">
         <v>44273</v>
       </c>
       <c r="F23" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G23" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="H23" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -2238,16 +2259,16 @@
         <v>180204.78</v>
       </c>
       <c r="D24" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E24" s="2">
         <v>44259</v>
       </c>
       <c r="F24" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H24" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -2261,16 +2282,16 @@
         <v>19994.32</v>
       </c>
       <c r="D25" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E25" s="2">
         <v>44280</v>
       </c>
       <c r="F25" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H25" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -2284,19 +2305,19 @@
         <v>17060.16</v>
       </c>
       <c r="D26" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E26" s="2">
         <v>44279</v>
       </c>
       <c r="F26" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="G26" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="H26" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -2310,16 +2331,16 @@
         <v>48008.41</v>
       </c>
       <c r="D27" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E27" s="2">
         <v>44279</v>
       </c>
       <c r="F27" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H27" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -2333,19 +2354,19 @@
         <v>14114.21</v>
       </c>
       <c r="D28" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E28" s="2">
         <v>44293</v>
       </c>
       <c r="F28" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="G28" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H28" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -2359,16 +2380,16 @@
         <v>12344.44</v>
       </c>
       <c r="D29" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E29" s="2">
         <v>44285</v>
       </c>
       <c r="F29" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H29" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -2382,16 +2403,16 @@
         <v>23323</v>
       </c>
       <c r="D30" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E30" s="2">
         <v>44281</v>
       </c>
       <c r="F30" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="H30" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2405,16 +2426,16 @@
         <v>143670.95</v>
       </c>
       <c r="D31" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E31" s="2">
         <v>44286</v>
       </c>
       <c r="F31" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H31" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -2428,16 +2449,16 @@
         <v>15000</v>
       </c>
       <c r="D32" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E32" s="2">
         <v>44300</v>
       </c>
       <c r="F32" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H32" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -2451,16 +2472,16 @@
         <v>15563.96</v>
       </c>
       <c r="D33" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E33" s="2">
         <v>44306</v>
       </c>
       <c r="F33" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="H33" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -2474,16 +2495,16 @@
         <v>42997.07</v>
       </c>
       <c r="D34" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E34" s="2">
         <v>44299</v>
       </c>
       <c r="F34" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="H34" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2497,16 +2518,16 @@
         <v>72038.67999999999</v>
       </c>
       <c r="D35" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E35" s="2">
         <v>44314</v>
       </c>
       <c r="F35" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H35" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -2520,16 +2541,16 @@
         <v>51618.2</v>
       </c>
       <c r="D36" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E36" s="2">
         <v>44315</v>
       </c>
       <c r="F36" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H36" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2543,16 +2564,16 @@
         <v>118122.86</v>
       </c>
       <c r="D37" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E37" s="2">
         <v>44315</v>
       </c>
       <c r="F37" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H37" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -2566,16 +2587,16 @@
         <v>101094.66</v>
       </c>
       <c r="D38" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E38" s="2">
         <v>44314</v>
       </c>
       <c r="F38" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H38" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -2589,16 +2610,16 @@
         <v>15511.36</v>
       </c>
       <c r="D39" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E39" s="2">
         <v>44326</v>
       </c>
       <c r="F39" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H39" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -2612,16 +2633,16 @@
         <v>144961.24</v>
       </c>
       <c r="D40" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E40" s="2">
         <v>44315</v>
       </c>
       <c r="F40" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="H40" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -2635,16 +2656,16 @@
         <v>109548</v>
       </c>
       <c r="D41" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E41" s="2">
         <v>44344</v>
       </c>
       <c r="F41" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H41" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -2658,16 +2679,16 @@
         <v>19589.49</v>
       </c>
       <c r="D42" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E42" s="2">
         <v>44336</v>
       </c>
       <c r="F42" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="H42" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2681,16 +2702,16 @@
         <v>33486.48</v>
       </c>
       <c r="D43" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E43" s="2">
         <v>44343</v>
       </c>
       <c r="F43" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H43" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2704,16 +2725,16 @@
         <v>74992</v>
       </c>
       <c r="D44" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E44" s="2">
         <v>44347</v>
       </c>
       <c r="F44" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H44" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -2727,16 +2748,16 @@
         <v>109791.88</v>
       </c>
       <c r="D45" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E45" s="2">
         <v>44347</v>
       </c>
       <c r="F45" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H45" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -2750,16 +2771,16 @@
         <v>24096</v>
       </c>
       <c r="D46" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E46" s="2">
         <v>44350</v>
       </c>
       <c r="F46" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H46" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -2773,16 +2794,16 @@
         <v>32894</v>
       </c>
       <c r="D47" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E47" s="2">
         <v>44363</v>
       </c>
       <c r="F47" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H47" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -2796,19 +2817,19 @@
         <v>90898.60000000001</v>
       </c>
       <c r="D48" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E48" s="2">
         <v>44348</v>
       </c>
       <c r="F48" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="G48" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="H48" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2822,16 +2843,16 @@
         <v>79410</v>
       </c>
       <c r="D49" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E49" s="2">
         <v>44355</v>
       </c>
       <c r="F49" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="H49" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -2848,10 +2869,10 @@
         <v>44355</v>
       </c>
       <c r="F50" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H50" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -2865,16 +2886,16 @@
         <v>30060</v>
       </c>
       <c r="D51" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E51" s="2">
         <v>44368</v>
       </c>
       <c r="F51" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H51" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -2888,16 +2909,16 @@
         <v>51608.6</v>
       </c>
       <c r="D52" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E52" s="2">
         <v>44368</v>
       </c>
       <c r="F52" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H52" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -2911,16 +2932,16 @@
         <v>49192.74</v>
       </c>
       <c r="D53" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E53" s="2">
         <v>44375</v>
       </c>
       <c r="F53" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H53" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2934,19 +2955,19 @@
         <v>47508</v>
       </c>
       <c r="D54" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E54" s="2">
         <v>44376</v>
       </c>
       <c r="F54" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="G54" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="H54" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2960,16 +2981,16 @@
         <v>32673</v>
       </c>
       <c r="D55" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E55" s="2">
         <v>44375</v>
       </c>
       <c r="F55" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H55" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2983,16 +3004,16 @@
         <v>48167</v>
       </c>
       <c r="D56" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E56" s="2">
         <v>44376</v>
       </c>
       <c r="F56" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H56" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -3006,16 +3027,16 @@
         <v>98778.67</v>
       </c>
       <c r="D57" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E57" s="2">
         <v>44376</v>
       </c>
       <c r="F57" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H57" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -3029,16 +3050,16 @@
         <v>21226.54</v>
       </c>
       <c r="D58" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E58" s="2">
         <v>44385</v>
       </c>
       <c r="F58" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H58" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -3052,19 +3073,19 @@
         <v>1018113</v>
       </c>
       <c r="D59" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E59" s="2">
         <v>44377</v>
       </c>
       <c r="F59" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="G59" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H59" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -3078,16 +3099,16 @@
         <v>145281</v>
       </c>
       <c r="D60" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="E60" s="2">
         <v>44376</v>
       </c>
       <c r="F60" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H60" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -3101,16 +3122,16 @@
         <v>437295</v>
       </c>
       <c r="D61" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E61" s="2">
         <v>44354</v>
       </c>
       <c r="F61" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H61" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -3124,19 +3145,19 @@
         <v>48600</v>
       </c>
       <c r="D62" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="E62" s="2">
         <v>44371</v>
       </c>
       <c r="F62" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="G62" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="H62" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -3150,19 +3171,19 @@
         <v>78696</v>
       </c>
       <c r="D63" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="E63" s="2">
         <v>44371</v>
       </c>
       <c r="F63" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="G63" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="H63" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -3176,16 +3197,16 @@
         <v>27360</v>
       </c>
       <c r="D64" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E64" s="2">
         <v>44407</v>
       </c>
       <c r="F64" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H64" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -3199,16 +3220,16 @@
         <v>54307</v>
       </c>
       <c r="D65" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E65" s="2">
         <v>44382</v>
       </c>
       <c r="F65" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H65" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -3222,16 +3243,16 @@
         <v>18049.5</v>
       </c>
       <c r="D66" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E66" s="2">
         <v>44410</v>
       </c>
       <c r="F66" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H66" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -3245,19 +3266,19 @@
         <v>426000</v>
       </c>
       <c r="D67" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="E67" s="2">
         <v>44374</v>
       </c>
       <c r="F67" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="G67" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H67" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -3271,16 +3292,16 @@
         <v>96164</v>
       </c>
       <c r="D68" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="E68" s="2">
         <v>44438</v>
       </c>
       <c r="F68" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H68" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -3294,19 +3315,19 @@
         <v>21660</v>
       </c>
       <c r="D69" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="E69" s="2">
         <v>44440</v>
       </c>
       <c r="F69" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="G69" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H69" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -3320,16 +3341,16 @@
         <v>164796</v>
       </c>
       <c r="D70" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E70" s="2">
         <v>44432</v>
       </c>
       <c r="F70" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H70" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -3343,16 +3364,16 @@
         <v>226636</v>
       </c>
       <c r="D71" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E71" s="2">
         <v>44439</v>
       </c>
       <c r="F71" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H71" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -3366,16 +3387,16 @@
         <v>18408</v>
       </c>
       <c r="D72" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E72" s="2">
         <v>44447</v>
       </c>
       <c r="F72" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H72" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -3389,16 +3410,16 @@
         <v>117341</v>
       </c>
       <c r="D73" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="E73" s="2">
         <v>44462</v>
       </c>
       <c r="F73" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H73" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -3412,16 +3433,16 @@
         <v>150297</v>
       </c>
       <c r="D74" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E74" s="2">
         <v>44461</v>
       </c>
       <c r="F74" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H74" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -3435,16 +3456,16 @@
         <v>25140.84</v>
       </c>
       <c r="D75" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E75" s="2">
         <v>44463</v>
       </c>
       <c r="F75" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H75" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -3458,16 +3479,16 @@
         <v>72578.35000000001</v>
       </c>
       <c r="D76" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E76" s="2">
         <v>44463</v>
       </c>
       <c r="F76" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H76" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -3481,16 +3502,16 @@
         <v>30000</v>
       </c>
       <c r="D77" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E77" s="2">
         <v>44454</v>
       </c>
       <c r="F77" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H77" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -3504,16 +3525,16 @@
         <v>72674.92</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E78" s="2">
         <v>44469</v>
       </c>
       <c r="F78" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H78" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -3527,16 +3548,16 @@
         <v>158752.08</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E79" s="2">
         <v>44483</v>
       </c>
       <c r="F79" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H79" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -3550,16 +3571,16 @@
         <v>36348</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E80" s="2">
         <v>44463</v>
       </c>
       <c r="F80" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H80" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -3573,16 +3594,16 @@
         <v>17258.07</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E81" s="2">
         <v>44489</v>
       </c>
       <c r="F81" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H81" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -3596,16 +3617,16 @@
         <v>36000</v>
       </c>
       <c r="D82" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E82" s="2">
         <v>44438</v>
       </c>
       <c r="F82" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H82" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -3619,19 +3640,19 @@
         <v>321844</v>
       </c>
       <c r="D83" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E83" s="2">
         <v>44438</v>
       </c>
       <c r="F83" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="G83" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H83" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -3645,16 +3666,16 @@
         <v>30320</v>
       </c>
       <c r="D84" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E84" s="2">
         <v>44483</v>
       </c>
       <c r="F84" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H84" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -3668,19 +3689,19 @@
         <v>61133.08</v>
       </c>
       <c r="D85" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E85" s="2">
         <v>44498</v>
       </c>
       <c r="F85" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="G85" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H85" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -3694,16 +3715,16 @@
         <v>97073.67</v>
       </c>
       <c r="D86" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E86" s="2">
         <v>44504</v>
       </c>
       <c r="F86" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H86" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -3717,16 +3738,16 @@
         <v>11524</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="E87" s="2">
         <v>44503</v>
       </c>
       <c r="F87" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H87" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -3740,16 +3761,16 @@
         <v>35463.96</v>
       </c>
       <c r="D88" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E88" s="2">
         <v>44498</v>
       </c>
       <c r="F88" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H88" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -3763,19 +3784,19 @@
         <v>120575.25</v>
       </c>
       <c r="D89" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E89" s="2">
         <v>44469</v>
       </c>
       <c r="F89" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="G89" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="H89" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -3789,19 +3810,19 @@
         <v>74156.7</v>
       </c>
       <c r="D90" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E90" s="2">
         <v>44509</v>
       </c>
       <c r="F90" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G90" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="H90" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -3815,16 +3836,16 @@
         <v>123014.81</v>
       </c>
       <c r="D91" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E91" s="2">
         <v>44518</v>
       </c>
       <c r="F91" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H91" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -3838,16 +3859,16 @@
         <v>97596.27</v>
       </c>
       <c r="D92" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E92" s="2">
         <v>44515</v>
       </c>
       <c r="F92" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H92" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -3861,16 +3882,16 @@
         <v>18103.47</v>
       </c>
       <c r="D93" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E93" s="2">
         <v>44523</v>
       </c>
       <c r="F93" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H93" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -3884,19 +3905,19 @@
         <v>21375.84</v>
       </c>
       <c r="D94" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="E94" s="2">
         <v>44505</v>
       </c>
       <c r="F94" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="G94" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H94" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -3910,16 +3931,16 @@
         <v>77675.48</v>
       </c>
       <c r="D95" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E95" s="2">
         <v>44498</v>
       </c>
       <c r="F95" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H95" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -3933,16 +3954,16 @@
         <v>137845</v>
       </c>
       <c r="D96" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E96" s="2">
         <v>44448</v>
       </c>
       <c r="F96" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H96" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3956,16 +3977,16 @@
         <v>387640</v>
       </c>
       <c r="D97" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E97" s="2">
         <v>44467</v>
       </c>
       <c r="F97" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H97" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3979,16 +4000,16 @@
         <v>118967</v>
       </c>
       <c r="D98" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E98" s="2">
         <v>44467</v>
       </c>
       <c r="F98" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H98" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -4002,16 +4023,16 @@
         <v>271848</v>
       </c>
       <c r="D99" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E99" s="2">
         <v>44467</v>
       </c>
       <c r="F99" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H99" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -4025,16 +4046,16 @@
         <v>65365</v>
       </c>
       <c r="D100" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E100" s="2">
         <v>44530</v>
       </c>
       <c r="F100" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H100" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -4048,16 +4069,16 @@
         <v>59696</v>
       </c>
       <c r="D101" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E101" s="2">
         <v>44531</v>
       </c>
       <c r="F101" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H101" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -4071,16 +4092,16 @@
         <v>18540</v>
       </c>
       <c r="D102" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E102" s="2">
         <v>44536</v>
       </c>
       <c r="F102" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="H102" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -4094,16 +4115,16 @@
         <v>33761</v>
       </c>
       <c r="D103" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E103" s="2">
         <v>44545</v>
       </c>
       <c r="G103" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H103" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -4117,16 +4138,16 @@
         <v>33034</v>
       </c>
       <c r="D104" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E104" s="2">
         <v>44498</v>
       </c>
       <c r="F104" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H104" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -4140,16 +4161,16 @@
         <v>162281</v>
       </c>
       <c r="D105" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E105" s="2">
         <v>44530</v>
       </c>
       <c r="F105" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H105" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -4163,16 +4184,16 @@
         <v>22438</v>
       </c>
       <c r="D106" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E106" s="2">
         <v>44546</v>
       </c>
       <c r="F106" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H106" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -4186,16 +4207,16 @@
         <v>18120</v>
       </c>
       <c r="D107" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="E107" s="2">
         <v>44498</v>
       </c>
       <c r="F107" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H107" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -4209,16 +4230,16 @@
         <v>37004</v>
       </c>
       <c r="D108" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E108" s="2">
         <v>44550</v>
       </c>
       <c r="F108" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H108" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -4232,16 +4253,16 @@
         <v>55692.36</v>
       </c>
       <c r="D109" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E109" s="2">
         <v>44540</v>
       </c>
       <c r="F109" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H109" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -4255,16 +4276,16 @@
         <v>58860</v>
       </c>
       <c r="D110" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E110" s="2">
         <v>44553</v>
       </c>
       <c r="F110" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H110" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -4278,16 +4299,16 @@
         <v>1724952</v>
       </c>
       <c r="D111" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="E111" s="2">
         <v>44494</v>
       </c>
       <c r="F111" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H111" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -4301,16 +4322,16 @@
         <v>156000</v>
       </c>
       <c r="D112" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="E112" s="2">
         <v>44466</v>
       </c>
       <c r="F112" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="H112" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -4324,16 +4345,16 @@
         <v>1783320</v>
       </c>
       <c r="D113" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E113" s="2">
         <v>44557</v>
       </c>
       <c r="F113" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H113" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -4347,19 +4368,19 @@
         <v>44529.04</v>
       </c>
       <c r="D114" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E114" s="2">
         <v>44583</v>
       </c>
       <c r="F114" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="G114" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="H114" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -4373,16 +4394,16 @@
         <v>195393.13</v>
       </c>
       <c r="D115" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E115" s="2">
         <v>44587</v>
       </c>
       <c r="F115" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="H115" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -4396,16 +4417,16 @@
         <v>16357.92</v>
       </c>
       <c r="D116" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E116" s="2">
         <v>44589</v>
       </c>
       <c r="F116" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H116" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -4419,19 +4440,19 @@
         <v>86395.57000000001</v>
       </c>
       <c r="D117" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E117" s="2">
         <v>44592</v>
       </c>
       <c r="F117" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="G117" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="H117" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -4445,16 +4466,16 @@
         <v>65843.74000000001</v>
       </c>
       <c r="D118" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E118" s="2">
         <v>44592</v>
       </c>
       <c r="F118" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="H118" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -4468,16 +4489,16 @@
         <v>44071.91</v>
       </c>
       <c r="D119" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E119" s="2">
         <v>44593</v>
       </c>
       <c r="F119" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H119" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -4491,16 +4512,16 @@
         <v>18108</v>
       </c>
       <c r="D120" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E120" s="2">
         <v>44594</v>
       </c>
       <c r="F120" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H120" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -4514,16 +4535,16 @@
         <v>123510</v>
       </c>
       <c r="D121" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E121" s="2">
         <v>44594</v>
       </c>
       <c r="F121" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H121" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -4537,16 +4558,16 @@
         <v>32379.56</v>
       </c>
       <c r="D122" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E122" s="2">
         <v>44599</v>
       </c>
       <c r="F122" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="H122" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -4560,19 +4581,19 @@
         <v>2206300</v>
       </c>
       <c r="D123" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E123" s="2">
         <v>44599</v>
       </c>
       <c r="F123" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="G123" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H123" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -4586,16 +4607,16 @@
         <v>59444.88</v>
       </c>
       <c r="D124" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E124" s="2">
         <v>44600</v>
       </c>
       <c r="F124" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H124" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -4609,16 +4630,16 @@
         <v>27046.56</v>
       </c>
       <c r="D125" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E125" s="2">
         <v>44601</v>
       </c>
       <c r="F125" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H125" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -4632,16 +4653,16 @@
         <v>78090</v>
       </c>
       <c r="D126" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E126" s="2">
         <v>44602</v>
       </c>
       <c r="F126" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H126" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -4655,16 +4676,16 @@
         <v>131316</v>
       </c>
       <c r="D127" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E127" s="2">
         <v>44609</v>
       </c>
       <c r="F127" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H127" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -4678,16 +4699,16 @@
         <v>26775.27</v>
       </c>
       <c r="D128" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E128" s="2">
         <v>44609</v>
       </c>
       <c r="F128" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H128" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -4701,16 +4722,16 @@
         <v>21714.47</v>
       </c>
       <c r="D129" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E129" s="2">
         <v>44615</v>
       </c>
       <c r="F129" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H129" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -4724,16 +4745,16 @@
         <v>284992.08</v>
       </c>
       <c r="D130" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E130" s="2">
         <v>44615</v>
       </c>
       <c r="F130" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H130" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -4747,16 +4768,16 @@
         <v>79981.99000000001</v>
       </c>
       <c r="D131" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E131" s="2">
         <v>44617</v>
       </c>
       <c r="F131" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H131" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -4770,16 +4791,16 @@
         <v>73747</v>
       </c>
       <c r="D132" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E132" s="2">
         <v>44617</v>
       </c>
       <c r="F132" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H132" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -4793,16 +4814,16 @@
         <v>154056.97</v>
       </c>
       <c r="D133" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E133" s="2">
         <v>44620</v>
       </c>
       <c r="F133" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H133" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -4816,16 +4837,16 @@
         <v>22255.93</v>
       </c>
       <c r="D134" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E134" s="2">
         <v>44620</v>
       </c>
       <c r="F134" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H134" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -4839,16 +4860,16 @@
         <v>12087</v>
       </c>
       <c r="D135" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="E135" s="2">
         <v>44620</v>
       </c>
       <c r="F135" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H135" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -4862,16 +4883,16 @@
         <v>229700</v>
       </c>
       <c r="D136" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E136" s="2">
         <v>44630</v>
       </c>
       <c r="F136" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H136" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -4885,16 +4906,16 @@
         <v>153000</v>
       </c>
       <c r="D137" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E137" s="2">
         <v>44631</v>
       </c>
       <c r="F137" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H137" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -4908,16 +4929,16 @@
         <v>4467</v>
       </c>
       <c r="D138" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E138" s="2">
         <v>44634</v>
       </c>
       <c r="F138" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H138" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -4931,16 +4952,16 @@
         <v>46500</v>
       </c>
       <c r="D139" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E139" s="2">
         <v>44637</v>
       </c>
       <c r="F139" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H139" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -4954,16 +4975,16 @@
         <v>113561</v>
       </c>
       <c r="D140" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E140" s="2">
         <v>44643</v>
       </c>
       <c r="F140" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H140" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -4977,16 +4998,16 @@
         <v>50075</v>
       </c>
       <c r="D141" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E141" s="2">
         <v>44645</v>
       </c>
       <c r="F141" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="H141" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -5000,16 +5021,16 @@
         <v>264132</v>
       </c>
       <c r="D142" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E142" s="2">
         <v>44645</v>
       </c>
       <c r="F142" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H142" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -5023,16 +5044,16 @@
         <v>95656.64999999999</v>
       </c>
       <c r="D143" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E143" s="2">
         <v>44649</v>
       </c>
       <c r="F143" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H143" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -5046,16 +5067,16 @@
         <v>19712.96</v>
       </c>
       <c r="D144" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E144" s="2">
         <v>44649</v>
       </c>
       <c r="F144" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H144" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -5069,16 +5090,16 @@
         <v>5520</v>
       </c>
       <c r="D145" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="E145" s="2">
         <v>44652</v>
       </c>
       <c r="F145" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H145" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -5092,19 +5113,19 @@
         <v>15000</v>
       </c>
       <c r="D146" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E146" s="2">
         <v>44655</v>
       </c>
       <c r="F146" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="G146" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H146" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -5118,16 +5139,16 @@
         <v>44929.04</v>
       </c>
       <c r="D147" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E147" s="2">
         <v>44655</v>
       </c>
       <c r="F147" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="H147" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -5141,16 +5162,16 @@
         <v>2164926</v>
       </c>
       <c r="D148" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E148" s="2">
         <v>44656</v>
       </c>
       <c r="F148" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H148" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -5164,16 +5185,16 @@
         <v>5500</v>
       </c>
       <c r="D149" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="E149" s="2">
         <v>44672</v>
       </c>
       <c r="F149" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H149" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -5187,16 +5208,16 @@
         <v>80534</v>
       </c>
       <c r="D150" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E150" s="2">
         <v>44681</v>
       </c>
       <c r="F150" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="H150" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -5210,16 +5231,16 @@
         <v>58657</v>
       </c>
       <c r="D151" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E151" s="2">
         <v>44685</v>
       </c>
       <c r="F151" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H151" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -5233,16 +5254,16 @@
         <v>259880</v>
       </c>
       <c r="D152" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E152" s="2">
         <v>44692</v>
       </c>
       <c r="F152" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H152" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -5256,16 +5277,16 @@
         <v>44851</v>
       </c>
       <c r="D153" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E153" s="2">
         <v>44719</v>
       </c>
       <c r="F153" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="H153" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -5279,16 +5300,16 @@
         <v>15000</v>
       </c>
       <c r="D154" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E154" s="2">
         <v>44719</v>
       </c>
       <c r="F154" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H154" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -5302,16 +5323,16 @@
         <v>36000</v>
       </c>
       <c r="D155" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E155" s="2">
         <v>44732</v>
       </c>
       <c r="F155" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H155" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -5325,16 +5346,16 @@
         <v>85765.3</v>
       </c>
       <c r="D156" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E156" s="2">
         <v>44736</v>
       </c>
       <c r="F156" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H156" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -5348,16 +5369,16 @@
         <v>41918.41</v>
       </c>
       <c r="D157" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E157" s="2">
         <v>44742</v>
       </c>
       <c r="F157" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H157" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -5371,16 +5392,16 @@
         <v>141922</v>
       </c>
       <c r="D158" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E158" s="2">
         <v>44742</v>
       </c>
       <c r="F158" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H158" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -5394,16 +5415,16 @@
         <v>36000</v>
       </c>
       <c r="D159" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="E159" s="2">
         <v>44742</v>
       </c>
       <c r="F159" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H159" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -5417,16 +5438,16 @@
         <v>53378.16</v>
       </c>
       <c r="D160" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E160" s="2">
         <v>44749</v>
       </c>
       <c r="F160" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H160" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -5440,16 +5461,16 @@
         <v>40191.95</v>
       </c>
       <c r="D161" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E161" s="2">
         <v>44753</v>
       </c>
       <c r="F161" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H161" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -5463,19 +5484,19 @@
         <v>33339.71</v>
       </c>
       <c r="D162" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E162" s="2">
         <v>44774</v>
       </c>
       <c r="F162" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="G162" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H162" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -5489,16 +5510,16 @@
         <v>12000</v>
       </c>
       <c r="D163" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E163" s="2">
         <v>44775</v>
       </c>
       <c r="F163" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H163" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -5512,16 +5533,16 @@
         <v>142246</v>
       </c>
       <c r="D164" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E164" s="2">
         <v>44783</v>
       </c>
       <c r="F164" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H164" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -5535,16 +5556,16 @@
         <v>57060</v>
       </c>
       <c r="D165" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="E165" s="2">
         <v>44784</v>
       </c>
       <c r="F165" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="H165" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -5558,16 +5579,16 @@
         <v>24581</v>
       </c>
       <c r="D166" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E166" s="2">
         <v>44810</v>
       </c>
       <c r="F166" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H166" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -5581,16 +5602,16 @@
         <v>61008</v>
       </c>
       <c r="D167" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E167" s="2">
         <v>44811</v>
       </c>
       <c r="F167" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H167" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -5604,16 +5625,16 @@
         <v>108824</v>
       </c>
       <c r="D168" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E168" s="2">
         <v>44816</v>
       </c>
       <c r="F168" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H168" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -5627,16 +5648,16 @@
         <v>18449</v>
       </c>
       <c r="D169" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E169" s="2">
         <v>44820</v>
       </c>
       <c r="F169" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H169" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -5650,10 +5671,10 @@
         <v>9000</v>
       </c>
       <c r="D170" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="F170" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -5667,16 +5688,16 @@
         <v>31068</v>
       </c>
       <c r="D171" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E171" s="2">
         <v>44831</v>
       </c>
       <c r="F171" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H171" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -5690,16 +5711,16 @@
         <v>48312</v>
       </c>
       <c r="D172" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E172" s="2">
         <v>44833</v>
       </c>
       <c r="F172" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H172" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -5713,16 +5734,16 @@
         <v>310116</v>
       </c>
       <c r="D173" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E173" s="2">
         <v>44823</v>
       </c>
       <c r="F173" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H173" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -5736,19 +5757,19 @@
         <v>145870</v>
       </c>
       <c r="D174" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E174" s="2">
         <v>44834</v>
       </c>
       <c r="F174" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="G174" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H174" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -5762,16 +5783,16 @@
         <v>61182</v>
       </c>
       <c r="D175" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E175" s="2">
         <v>44858</v>
       </c>
       <c r="F175" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H175" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -5785,16 +5806,16 @@
         <v>564456</v>
       </c>
       <c r="D176" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E176" s="2">
         <v>44834</v>
       </c>
       <c r="F176" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H176" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -5808,16 +5829,16 @@
         <v>15360</v>
       </c>
       <c r="D177" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E177" s="2">
         <v>44852</v>
       </c>
       <c r="F177" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H177" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -5831,16 +5852,16 @@
         <v>75638</v>
       </c>
       <c r="D178" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E178" s="2">
         <v>44858</v>
       </c>
       <c r="F178" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H178" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -5854,16 +5875,16 @@
         <v>17098</v>
       </c>
       <c r="D179" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E179" s="2">
         <v>44861</v>
       </c>
       <c r="F179" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H179" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -5877,16 +5898,16 @@
         <v>47117</v>
       </c>
       <c r="D180" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E180" s="2">
         <v>44862</v>
       </c>
       <c r="F180" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H180" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -5900,16 +5921,16 @@
         <v>71046</v>
       </c>
       <c r="D181" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E181" s="2">
         <v>44865</v>
       </c>
       <c r="F181" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H181" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -5923,16 +5944,16 @@
         <v>16796</v>
       </c>
       <c r="D182" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="E182" s="2">
         <v>44865</v>
       </c>
       <c r="F182" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H182" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -5946,16 +5967,16 @@
         <v>30806</v>
       </c>
       <c r="D183" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="E183" s="2">
         <v>44868</v>
       </c>
       <c r="F183" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H183" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -5969,16 +5990,16 @@
         <v>42583</v>
       </c>
       <c r="D184" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E184" s="2">
         <v>44872</v>
       </c>
       <c r="F184" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="H184" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -5992,16 +6013,16 @@
         <v>15000</v>
       </c>
       <c r="D185" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E185" s="2">
         <v>44837</v>
       </c>
       <c r="F185" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="H185" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -6015,16 +6036,16 @@
         <v>20172</v>
       </c>
       <c r="D186" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E186" s="2">
         <v>44873</v>
       </c>
       <c r="F186" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H186" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -6038,19 +6059,19 @@
         <v>1033505</v>
       </c>
       <c r="D187" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E187" s="2">
         <v>44891</v>
       </c>
       <c r="F187" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G187" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="H187" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -6064,19 +6085,19 @@
         <v>101508</v>
       </c>
       <c r="D188" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E188" s="2">
         <v>44875</v>
       </c>
       <c r="F188" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="G188" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H188" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -6090,16 +6111,16 @@
         <v>219234</v>
       </c>
       <c r="D189" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E189" s="2">
         <v>44881</v>
       </c>
       <c r="F189" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="H189" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -6113,16 +6134,16 @@
         <v>19647</v>
       </c>
       <c r="D190" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E190" s="2">
         <v>44866</v>
       </c>
       <c r="F190" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H190" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -6136,16 +6157,16 @@
         <v>289659</v>
       </c>
       <c r="D191" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E191" s="2">
         <v>44890</v>
       </c>
       <c r="F191" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H191" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -6159,16 +6180,16 @@
         <v>44550</v>
       </c>
       <c r="D192" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E192" s="2">
         <v>44894</v>
       </c>
       <c r="F192" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H192" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="193" spans="1:8">
@@ -6182,16 +6203,16 @@
         <v>50482.04</v>
       </c>
       <c r="D193" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="E193" s="2">
         <v>44831</v>
       </c>
       <c r="F193" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H193" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -6205,16 +6226,16 @@
         <v>186313</v>
       </c>
       <c r="D194" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E194" s="2">
         <v>44895</v>
       </c>
       <c r="F194" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H194" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -6228,16 +6249,16 @@
         <v>3432</v>
       </c>
       <c r="D195" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="E195" s="2">
         <v>44895</v>
       </c>
       <c r="F195" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H195" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -6251,16 +6272,16 @@
         <v>24000</v>
       </c>
       <c r="D196" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E196" s="2">
         <v>44895</v>
       </c>
       <c r="F196" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H196" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="197" spans="1:8">
@@ -6274,16 +6295,16 @@
         <v>6072</v>
       </c>
       <c r="D197" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E197" s="2">
         <v>44915</v>
       </c>
       <c r="F197" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H197" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -6297,19 +6318,19 @@
         <v>90042.39999999999</v>
       </c>
       <c r="D198" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E198" s="2">
         <v>44916</v>
       </c>
       <c r="F198" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="G198" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="H198" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -6323,13 +6344,13 @@
         <v>4512</v>
       </c>
       <c r="D199" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E199" s="2">
         <v>44928</v>
       </c>
       <c r="H199" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -6343,16 +6364,16 @@
         <v>52852.17</v>
       </c>
       <c r="D200" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E200" s="2">
         <v>44936</v>
       </c>
       <c r="G200" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H200" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -6366,13 +6387,13 @@
         <v>150188</v>
       </c>
       <c r="D201" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E201" s="2">
         <v>44939</v>
       </c>
       <c r="H201" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -6386,13 +6407,13 @@
         <v>43967</v>
       </c>
       <c r="D202" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E202" s="2">
         <v>44904</v>
       </c>
       <c r="H202" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -6406,13 +6427,13 @@
         <v>199392.4</v>
       </c>
       <c r="D203" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E203" s="2">
         <v>44950</v>
       </c>
       <c r="H203" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -6426,13 +6447,13 @@
         <v>6137</v>
       </c>
       <c r="D204" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E204" s="2">
         <v>44951</v>
       </c>
       <c r="H204" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -6446,7 +6467,7 @@
         <v>128134</v>
       </c>
       <c r="D205" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -6460,13 +6481,13 @@
         <v>461390</v>
       </c>
       <c r="D206" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E206" s="2">
         <v>44952</v>
       </c>
       <c r="H206" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -6480,13 +6501,13 @@
         <v>26321.24</v>
       </c>
       <c r="D207" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E207" s="2">
         <v>44957</v>
       </c>
       <c r="H207" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -6500,13 +6521,13 @@
         <v>32723</v>
       </c>
       <c r="D208" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E208" s="2">
         <v>44956</v>
       </c>
       <c r="H208" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -6520,13 +6541,13 @@
         <v>31122</v>
       </c>
       <c r="D209" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E209" s="2">
         <v>44953</v>
       </c>
       <c r="H209" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -6540,13 +6561,13 @@
         <v>35483</v>
       </c>
       <c r="D210" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E210" s="2">
         <v>44953</v>
       </c>
       <c r="H210" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -6560,13 +6581,13 @@
         <v>179010</v>
       </c>
       <c r="D211" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E211" s="2">
         <v>44972</v>
       </c>
       <c r="H211" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -6580,13 +6601,13 @@
         <v>207498.12</v>
       </c>
       <c r="D212" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E212" s="2">
         <v>44978</v>
       </c>
       <c r="H212" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -6600,13 +6621,13 @@
         <v>99798</v>
       </c>
       <c r="D213" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E213" s="2">
         <v>44979</v>
       </c>
       <c r="H213" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -6620,13 +6641,13 @@
         <v>6564</v>
       </c>
       <c r="D214" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E214" s="2">
         <v>44979</v>
       </c>
       <c r="H214" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -6640,13 +6661,13 @@
         <v>303998.52</v>
       </c>
       <c r="D215" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E215" s="2">
         <v>44984</v>
       </c>
       <c r="H215" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -6660,13 +6681,13 @@
         <v>160611</v>
       </c>
       <c r="D216" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="E216" s="2">
         <v>45014</v>
       </c>
       <c r="H216" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -6680,13 +6701,13 @@
         <v>58165</v>
       </c>
       <c r="D217" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E217" s="2">
         <v>45009</v>
       </c>
       <c r="H217" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -6700,13 +6721,13 @@
         <v>74171</v>
       </c>
       <c r="D218" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E218" s="2">
         <v>45015</v>
       </c>
       <c r="H218" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -6720,13 +6741,13 @@
         <v>4513</v>
       </c>
       <c r="D219" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E219" s="2">
         <v>45027</v>
       </c>
       <c r="H219" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="220" spans="1:8">
@@ -6740,13 +6761,13 @@
         <v>132194</v>
       </c>
       <c r="D220" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E220" s="2">
         <v>45035</v>
       </c>
       <c r="H220" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -6760,13 +6781,13 @@
         <v>71414.8</v>
       </c>
       <c r="D221" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E221" s="2">
         <v>45029</v>
       </c>
       <c r="H221" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="222" spans="1:8">
@@ -6780,13 +6801,13 @@
         <v>32046.79</v>
       </c>
       <c r="D222" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E222" s="2">
         <v>45043</v>
       </c>
       <c r="H222" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="223" spans="1:8">
@@ -6800,13 +6821,13 @@
         <v>110646</v>
       </c>
       <c r="D223" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E223" s="2">
         <v>45047</v>
       </c>
       <c r="H223" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="224" spans="1:8">
@@ -6820,13 +6841,13 @@
         <v>71077.63</v>
       </c>
       <c r="D224" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E224" s="2">
         <v>45047</v>
       </c>
       <c r="H224" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="225" spans="1:8">
@@ -6840,13 +6861,13 @@
         <v>18378</v>
       </c>
       <c r="D225" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="E225" s="2">
         <v>45048</v>
       </c>
       <c r="H225" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="226" spans="1:8">
@@ -6860,13 +6881,13 @@
         <v>171628</v>
       </c>
       <c r="D226" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="E226" s="2">
         <v>45043</v>
       </c>
       <c r="H226" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -6880,13 +6901,13 @@
         <v>303577</v>
       </c>
       <c r="D227" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="E227" s="2">
         <v>45020</v>
       </c>
       <c r="H227" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="228" spans="1:8">
@@ -6900,13 +6921,13 @@
         <v>6277</v>
       </c>
       <c r="D228" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E228" s="2">
         <v>45048</v>
       </c>
       <c r="H228" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="229" spans="1:8">
@@ -6920,13 +6941,13 @@
         <v>125865</v>
       </c>
       <c r="D229" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="E229" s="2">
         <v>45044</v>
       </c>
       <c r="H229" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="230" spans="1:8">
@@ -6940,13 +6961,13 @@
         <v>236370</v>
       </c>
       <c r="D230" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E230" s="2">
         <v>45043</v>
       </c>
       <c r="H230" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="231" spans="1:8">
@@ -6960,13 +6981,13 @@
         <v>140432</v>
       </c>
       <c r="D231" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E231" s="2">
         <v>45061</v>
       </c>
       <c r="H231" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="232" spans="1:8">
@@ -6980,13 +7001,13 @@
         <v>19908</v>
       </c>
       <c r="D232" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E232" s="2">
         <v>45057</v>
       </c>
       <c r="H232" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="233" spans="1:8">
@@ -7000,13 +7021,13 @@
         <v>30453</v>
       </c>
       <c r="D233" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E233" s="2">
         <v>45070</v>
       </c>
       <c r="H233" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="234" spans="1:8">
@@ -7020,13 +7041,13 @@
         <v>104340</v>
       </c>
       <c r="D234" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="E234" s="2">
         <v>45070</v>
       </c>
       <c r="H234" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -7040,13 +7061,13 @@
         <v>76044</v>
       </c>
       <c r="D235" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E235" s="2">
         <v>45072</v>
       </c>
       <c r="H235" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -7060,13 +7081,13 @@
         <v>57600</v>
       </c>
       <c r="D236" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="E236" s="2">
         <v>45072</v>
       </c>
       <c r="H236" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -7080,13 +7101,13 @@
         <v>80135</v>
       </c>
       <c r="D237" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E237" s="2">
         <v>45076</v>
       </c>
       <c r="H237" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -7100,13 +7121,13 @@
         <v>23352</v>
       </c>
       <c r="D238" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="E238" s="2">
         <v>45090</v>
       </c>
       <c r="H238" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -7120,13 +7141,13 @@
         <v>46106</v>
       </c>
       <c r="D239" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E239" s="2">
         <v>45091</v>
       </c>
       <c r="H239" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -7140,13 +7161,13 @@
         <v>44064</v>
       </c>
       <c r="D240" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E240" s="2">
         <v>45092</v>
       </c>
       <c r="H240" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -7160,13 +7181,13 @@
         <v>32832</v>
       </c>
       <c r="D241" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="E241" s="2">
         <v>45092</v>
       </c>
       <c r="H241" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -7180,13 +7201,13 @@
         <v>19530</v>
       </c>
       <c r="D242" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E242" s="2">
         <v>45083</v>
       </c>
       <c r="H242" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -7200,13 +7221,13 @@
         <v>19908</v>
       </c>
       <c r="D243" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E243" s="2">
         <v>45091</v>
       </c>
       <c r="H243" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="244" spans="1:8">
@@ -7220,13 +7241,13 @@
         <v>100068</v>
       </c>
       <c r="D244" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E244" s="2">
         <v>45113</v>
       </c>
       <c r="H244" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -7240,13 +7261,13 @@
         <v>74972.74000000001</v>
       </c>
       <c r="D245" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E245" s="2">
         <v>45104</v>
       </c>
       <c r="H245" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -7260,16 +7281,16 @@
         <v>6371</v>
       </c>
       <c r="D246" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E246" s="2">
         <v>45106</v>
       </c>
       <c r="G246" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="H246" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="247" spans="1:8">
@@ -7283,13 +7304,13 @@
         <v>98144</v>
       </c>
       <c r="D247" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="E247" s="2">
         <v>45106</v>
       </c>
       <c r="H247" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -7303,13 +7324,13 @@
         <v>174121</v>
       </c>
       <c r="D248" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="E248" s="2">
         <v>45112</v>
       </c>
       <c r="H248" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="249" spans="1:8">
@@ -7323,13 +7344,13 @@
         <v>38576</v>
       </c>
       <c r="D249" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E249" s="2">
         <v>45114</v>
       </c>
       <c r="H249" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="250" spans="1:8">
@@ -7343,13 +7364,13 @@
         <v>25546.77</v>
       </c>
       <c r="D250" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E250" s="2">
         <v>45103</v>
       </c>
       <c r="H250" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="251" spans="1:8">
@@ -7363,13 +7384,13 @@
         <v>193200.15</v>
       </c>
       <c r="D251" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E251" s="2">
         <v>45103</v>
       </c>
       <c r="H251" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="252" spans="1:8">
@@ -7383,13 +7404,13 @@
         <v>87298.83</v>
       </c>
       <c r="D252" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E252" s="2">
         <v>45145</v>
       </c>
       <c r="H252" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="253" spans="1:8">
@@ -7403,13 +7424,13 @@
         <v>70780</v>
       </c>
       <c r="D253" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E253" s="2">
         <v>45145</v>
       </c>
       <c r="H253" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="254" spans="1:8">
@@ -7423,13 +7444,13 @@
         <v>6320</v>
       </c>
       <c r="D254" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E254" s="2">
         <v>45155</v>
       </c>
       <c r="H254" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="255" spans="1:8">
@@ -7443,13 +7464,13 @@
         <v>795170.24</v>
       </c>
       <c r="D255" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E255" s="2">
         <v>45154</v>
       </c>
       <c r="H255" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="256" spans="1:8">
@@ -7463,13 +7484,13 @@
         <v>129827.5</v>
       </c>
       <c r="D256" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E256" s="2">
         <v>45160</v>
       </c>
       <c r="H256" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="257" spans="1:8">
@@ -7483,13 +7504,13 @@
         <v>58800</v>
       </c>
       <c r="D257" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E257" s="2">
         <v>45167</v>
       </c>
       <c r="H257" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="258" spans="1:8">
@@ -7503,13 +7524,13 @@
         <v>278110</v>
       </c>
       <c r="D258" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E258" s="2">
         <v>45112</v>
       </c>
       <c r="H258" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="259" spans="1:8">
@@ -7523,16 +7544,16 @@
         <v>75401.86</v>
       </c>
       <c r="D259" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E259" s="2">
         <v>45167</v>
       </c>
       <c r="G259" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H259" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="260" spans="1:8">
@@ -7546,13 +7567,13 @@
         <v>129351.38</v>
       </c>
       <c r="D260" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E260" s="2">
         <v>45169</v>
       </c>
       <c r="H260" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -7566,13 +7587,13 @@
         <v>146634</v>
       </c>
       <c r="D261" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="E261" s="2">
         <v>45169</v>
       </c>
       <c r="H261" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -7586,13 +7607,13 @@
         <v>95742</v>
       </c>
       <c r="D262" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E262" s="2">
         <v>45169</v>
       </c>
       <c r="H262" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -7606,16 +7627,16 @@
         <v>44547</v>
       </c>
       <c r="D263" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E263" s="2">
         <v>45177</v>
       </c>
       <c r="G263" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="H263" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -7629,13 +7650,13 @@
         <v>69120</v>
       </c>
       <c r="D264" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E264" s="2">
         <v>45044</v>
       </c>
       <c r="H264" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -7649,16 +7670,16 @@
         <v>21650.08</v>
       </c>
       <c r="D265" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E265" s="2">
         <v>45182</v>
       </c>
       <c r="G265" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="H265" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="266" spans="1:8">
@@ -7672,13 +7693,13 @@
         <v>120288</v>
       </c>
       <c r="D266" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E266" s="2">
         <v>45183</v>
       </c>
       <c r="H266" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -7692,16 +7713,16 @@
         <v>102035.85</v>
       </c>
       <c r="D267" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E267" s="2">
         <v>45196</v>
       </c>
       <c r="G267" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H267" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -7715,16 +7736,16 @@
         <v>83103.05</v>
       </c>
       <c r="D268" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E268" s="2">
         <v>45198</v>
       </c>
       <c r="G268" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H268" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -7738,16 +7759,16 @@
         <v>28521.38</v>
       </c>
       <c r="D269" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E269" s="2">
         <v>45205</v>
       </c>
       <c r="G269" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H269" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -7761,16 +7782,16 @@
         <v>30097</v>
       </c>
       <c r="D270" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E270" s="2">
         <v>45205</v>
       </c>
       <c r="G270" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H270" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -7784,16 +7805,16 @@
         <v>85832.52</v>
       </c>
       <c r="D271" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E271" s="2">
         <v>45205</v>
       </c>
       <c r="G271" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="H271" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -7807,13 +7828,13 @@
         <v>60860</v>
       </c>
       <c r="D272" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E272" s="2">
         <v>45168</v>
       </c>
       <c r="H272" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -7827,13 +7848,13 @@
         <v>65688</v>
       </c>
       <c r="D273" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E273" s="2">
         <v>45211</v>
       </c>
       <c r="H273" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -7847,13 +7868,13 @@
         <v>39408</v>
       </c>
       <c r="D274" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E274" s="2">
         <v>45211</v>
       </c>
       <c r="H274" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -7867,16 +7888,16 @@
         <v>132000</v>
       </c>
       <c r="D275" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E275" s="2">
         <v>45230</v>
       </c>
       <c r="G275" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="H275" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -7890,13 +7911,13 @@
         <v>116715</v>
       </c>
       <c r="D276" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E276" s="2">
         <v>45212</v>
       </c>
       <c r="H276" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -7910,13 +7931,13 @@
         <v>269403</v>
       </c>
       <c r="D277" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="E277" s="2">
         <v>45226</v>
       </c>
       <c r="H277" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="278" spans="1:8">
@@ -7930,16 +7951,16 @@
         <v>20783.82</v>
       </c>
       <c r="D278" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E278" s="2">
         <v>45236</v>
       </c>
       <c r="G278" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="H278" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="279" spans="1:8">
@@ -7953,13 +7974,13 @@
         <v>128494</v>
       </c>
       <c r="D279" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="E279" s="2">
         <v>45231</v>
       </c>
       <c r="H279" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -7973,13 +7994,13 @@
         <v>20165</v>
       </c>
       <c r="D280" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E280" s="2">
         <v>45239</v>
       </c>
       <c r="H280" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -7993,16 +8014,16 @@
         <v>163235.74</v>
       </c>
       <c r="D281" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E281" s="2">
         <v>45243</v>
       </c>
       <c r="G281" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="H281" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="282" spans="1:8">
@@ -8016,16 +8037,16 @@
         <v>40172</v>
       </c>
       <c r="D282" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E282" s="2">
         <v>45243</v>
       </c>
       <c r="G282" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="H282" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="283" spans="1:8">
@@ -8039,13 +8060,13 @@
         <v>19776</v>
       </c>
       <c r="D283" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E283" s="2">
         <v>45233</v>
       </c>
       <c r="H283" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -8059,13 +8080,13 @@
         <v>23777</v>
       </c>
       <c r="D284" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E284" s="2">
         <v>45257</v>
       </c>
       <c r="H284" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="285" spans="1:8">
@@ -8079,13 +8100,13 @@
         <v>31857</v>
       </c>
       <c r="D285" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E285" s="2">
         <v>45245</v>
       </c>
       <c r="H285" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="286" spans="1:8">
@@ -8099,16 +8120,16 @@
         <v>23375</v>
       </c>
       <c r="D286" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E286" s="2">
         <v>45275</v>
       </c>
       <c r="G286" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="H286" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="287" spans="1:8">
@@ -8122,13 +8143,13 @@
         <v>109559.83</v>
       </c>
       <c r="D287" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E287" s="2">
         <v>45245</v>
       </c>
       <c r="H287" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -8142,16 +8163,16 @@
         <v>22553</v>
       </c>
       <c r="D288" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E288" s="2">
         <v>45268</v>
       </c>
       <c r="G288" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H288" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="289" spans="1:8">
@@ -8165,13 +8186,13 @@
         <v>40892</v>
       </c>
       <c r="D289" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E289" s="2">
         <v>45272</v>
       </c>
       <c r="H289" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="290" spans="1:8">
@@ -8185,13 +8206,13 @@
         <v>128519</v>
       </c>
       <c r="D290" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="E290" s="2">
         <v>45279</v>
       </c>
       <c r="H290" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="291" spans="1:8">
@@ -8205,13 +8226,13 @@
         <v>24550</v>
       </c>
       <c r="D291" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E291" s="2">
         <v>45281</v>
       </c>
       <c r="H291" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -8225,13 +8246,13 @@
         <v>80850</v>
       </c>
       <c r="D292" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E292" s="2">
         <v>45281</v>
       </c>
       <c r="H292" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -8245,13 +8266,13 @@
         <v>20119</v>
       </c>
       <c r="D293" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E293" s="2">
         <v>45289</v>
       </c>
       <c r="H293" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -8265,13 +8286,13 @@
         <v>76625</v>
       </c>
       <c r="D294" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E294" s="2">
         <v>45301</v>
       </c>
       <c r="H294" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -8285,13 +8306,13 @@
         <v>40925</v>
       </c>
       <c r="D295" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E295" s="2">
         <v>45301</v>
       </c>
       <c r="H295" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -8305,13 +8326,13 @@
         <v>481884</v>
       </c>
       <c r="D296" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E296" s="2">
         <v>45411</v>
       </c>
       <c r="H296" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -8325,16 +8346,16 @@
         <v>396212.06</v>
       </c>
       <c r="D297" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E297" s="2">
         <v>45322</v>
       </c>
       <c r="G297" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H297" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -8348,13 +8369,13 @@
         <v>59316</v>
       </c>
       <c r="D298" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E298" s="2">
         <v>45345</v>
       </c>
       <c r="H298" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -8368,13 +8389,13 @@
         <v>334560</v>
       </c>
       <c r="D299" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E299" s="2">
         <v>45407</v>
       </c>
       <c r="H299" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -8388,16 +8409,16 @@
         <v>299164.71</v>
       </c>
       <c r="D300" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E300" s="2">
         <v>45349</v>
       </c>
       <c r="G300" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H300" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -8411,16 +8432,16 @@
         <v>835734</v>
       </c>
       <c r="D301" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E301" s="2">
         <v>45351</v>
       </c>
       <c r="G301" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H301" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -8434,13 +8455,13 @@
         <v>215092.8</v>
       </c>
       <c r="D302" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E302" s="2">
         <v>45412</v>
       </c>
       <c r="H302" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -8454,16 +8475,16 @@
         <v>207826.07</v>
       </c>
       <c r="D303" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E303" s="2">
         <v>45349</v>
       </c>
       <c r="G303" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="H303" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -8477,16 +8498,16 @@
         <v>190188</v>
       </c>
       <c r="D304" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E304" s="2">
         <v>45442</v>
       </c>
       <c r="G304" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="H304" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -8500,13 +8521,13 @@
         <v>498945</v>
       </c>
       <c r="D305" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E305" s="2">
         <v>45357</v>
       </c>
       <c r="H305" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -8520,13 +8541,13 @@
         <v>175476</v>
       </c>
       <c r="D306" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E306" s="2">
         <v>45428</v>
       </c>
       <c r="H306" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="307" spans="1:8">
@@ -8540,16 +8561,16 @@
         <v>141595.93</v>
       </c>
       <c r="D307" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E307" s="2">
         <v>45442</v>
       </c>
       <c r="G307" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="H307" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="308" spans="1:8">
@@ -8563,13 +8584,13 @@
         <v>32083.08</v>
       </c>
       <c r="D308" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E308" s="2">
         <v>45359</v>
       </c>
       <c r="H308" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="309" spans="1:8">
@@ -8583,13 +8604,13 @@
         <v>127477</v>
       </c>
       <c r="D309" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="E309" s="2">
         <v>45295</v>
       </c>
       <c r="H309" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="310" spans="1:8">
@@ -8603,13 +8624,13 @@
         <v>113993.82</v>
       </c>
       <c r="D310" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E310" s="2">
         <v>45363</v>
       </c>
       <c r="H310" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="311" spans="1:8">
@@ -8623,13 +8644,13 @@
         <v>101832</v>
       </c>
       <c r="D311" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="E311" s="2">
         <v>45438</v>
       </c>
       <c r="H311" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="312" spans="1:8">
@@ -8643,13 +8664,13 @@
         <v>47491.62</v>
       </c>
       <c r="D312" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E312" s="2">
         <v>45370</v>
       </c>
       <c r="H312" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="313" spans="1:8">
@@ -8663,13 +8684,13 @@
         <v>74419</v>
       </c>
       <c r="D313" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E313" s="2">
         <v>45306</v>
       </c>
       <c r="H313" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="314" spans="1:8">
@@ -8683,13 +8704,13 @@
         <v>66672</v>
       </c>
       <c r="D314" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E314" s="2">
         <v>45407</v>
       </c>
       <c r="H314" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="315" spans="1:8">
@@ -8703,16 +8724,16 @@
         <v>16783.1</v>
       </c>
       <c r="D315" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E315" s="2">
         <v>45372</v>
       </c>
       <c r="G315" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="H315" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="316" spans="1:8">
@@ -8726,16 +8747,16 @@
         <v>186200</v>
       </c>
       <c r="D316" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E316" s="2">
         <v>45373</v>
       </c>
       <c r="G316" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H316" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="317" spans="1:8">
@@ -8749,13 +8770,13 @@
         <v>50892</v>
       </c>
       <c r="D317" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E317" s="2">
         <v>45400</v>
       </c>
       <c r="H317" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="318" spans="1:8">
@@ -8769,13 +8790,13 @@
         <v>218081.92</v>
       </c>
       <c r="D318" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E318" s="2">
         <v>45386</v>
       </c>
       <c r="H318" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="319" spans="1:8">
@@ -8789,16 +8810,16 @@
         <v>49332</v>
       </c>
       <c r="D319" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E319" s="2">
         <v>45433</v>
       </c>
       <c r="G319" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="H319" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="320" spans="1:8">
@@ -8812,16 +8833,16 @@
         <v>140256.16</v>
       </c>
       <c r="D320" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E320" s="2">
         <v>45399</v>
       </c>
       <c r="G320" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="H320" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="321" spans="1:8">
@@ -8835,13 +8856,13 @@
         <v>40956</v>
       </c>
       <c r="D321" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E321" s="2">
         <v>45329</v>
       </c>
       <c r="H321" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="322" spans="1:8">
@@ -8855,13 +8876,13 @@
         <v>18300</v>
       </c>
       <c r="D322" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E322" s="2">
         <v>45400</v>
       </c>
       <c r="H322" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -8875,13 +8896,13 @@
         <v>36672</v>
       </c>
       <c r="D323" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E323" s="2">
         <v>45293</v>
       </c>
       <c r="H323" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -8895,13 +8916,13 @@
         <v>33984</v>
       </c>
       <c r="D324" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E324" s="2">
         <v>45446</v>
       </c>
       <c r="H324" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -8915,16 +8936,16 @@
         <v>25747.01</v>
       </c>
       <c r="D325" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E325" s="2">
         <v>45420</v>
       </c>
       <c r="G325" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H325" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -8938,13 +8959,13 @@
         <v>31550</v>
       </c>
       <c r="D326" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="E326" s="2">
         <v>45232</v>
       </c>
       <c r="H326" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -8958,13 +8979,13 @@
         <v>360000</v>
       </c>
       <c r="D327" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E327" s="2">
         <v>45426</v>
       </c>
       <c r="H327" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -8978,16 +8999,16 @@
         <v>29760</v>
       </c>
       <c r="D328" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E328" s="2">
         <v>45429</v>
       </c>
       <c r="G328" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H328" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="329" spans="1:8">
@@ -9001,16 +9022,16 @@
         <v>25056</v>
       </c>
       <c r="D329" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E329" s="2">
         <v>45432</v>
       </c>
       <c r="G329" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="H329" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="330" spans="1:8">
@@ -9024,13 +9045,13 @@
         <v>21012</v>
       </c>
       <c r="D330" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E330" s="2">
         <v>45448</v>
       </c>
       <c r="H330" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="331" spans="1:8">
@@ -9044,13 +9065,13 @@
         <v>19350</v>
       </c>
       <c r="D331" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E331" s="2">
         <v>45436</v>
       </c>
       <c r="H331" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="332" spans="1:8">
@@ -9064,13 +9085,13 @@
         <v>59832</v>
       </c>
       <c r="D332" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E332" s="2">
         <v>45446</v>
       </c>
       <c r="H332" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -9084,16 +9105,16 @@
         <v>50400</v>
       </c>
       <c r="D333" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E333" s="2">
         <v>45447</v>
       </c>
       <c r="G333" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="H333" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="334" spans="1:8">
@@ -9107,13 +9128,13 @@
         <v>6708.12</v>
       </c>
       <c r="D334" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E334" s="2">
         <v>45378</v>
       </c>
       <c r="H334" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="335" spans="1:8">
@@ -9127,13 +9148,13 @@
         <v>129216</v>
       </c>
       <c r="D335" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E335" s="2">
         <v>45450</v>
       </c>
       <c r="H335" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="336" spans="1:8">
@@ -9147,13 +9168,13 @@
         <v>37272</v>
       </c>
       <c r="D336" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E336" s="2">
         <v>45453</v>
       </c>
       <c r="H336" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="337" spans="1:8">
@@ -9167,13 +9188,13 @@
         <v>20388</v>
       </c>
       <c r="D337" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E337" s="2">
         <v>45456</v>
       </c>
       <c r="H337" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="338" spans="1:8">
@@ -9187,13 +9208,13 @@
         <v>5000</v>
       </c>
       <c r="D338" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E338" s="2">
         <v>45457</v>
       </c>
       <c r="H338" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="339" spans="1:8">
@@ -9207,13 +9228,13 @@
         <v>35004</v>
       </c>
       <c r="D339" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E339" s="2">
         <v>45467</v>
       </c>
       <c r="H339" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="340" spans="1:8">
@@ -9227,16 +9248,16 @@
         <v>78804</v>
       </c>
       <c r="D340" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E340" s="2">
         <v>45469</v>
       </c>
       <c r="G340" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="H340" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="341" spans="1:8">
@@ -9250,16 +9271,16 @@
         <v>146340</v>
       </c>
       <c r="D341" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E341" s="2">
         <v>45462</v>
       </c>
       <c r="G341" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="H341" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="342" spans="1:8">
@@ -9273,13 +9294,13 @@
         <v>191400</v>
       </c>
       <c r="D342" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E342" s="2">
         <v>45476</v>
       </c>
       <c r="H342" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="343" spans="1:8">
@@ -9293,13 +9314,13 @@
         <v>55116</v>
       </c>
       <c r="D343" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E343" s="2">
         <v>45488</v>
       </c>
       <c r="H343" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="344" spans="1:8">
@@ -9313,13 +9334,13 @@
         <v>41460</v>
       </c>
       <c r="D344" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E344" s="2">
         <v>45516</v>
       </c>
       <c r="H344" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="345" spans="1:8">
@@ -9333,13 +9354,13 @@
         <v>40152</v>
       </c>
       <c r="D345" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E345" s="2">
         <v>45467</v>
       </c>
       <c r="H345" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="346" spans="1:8">
@@ -9353,13 +9374,13 @@
         <v>83544</v>
       </c>
       <c r="D346" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E346" s="2">
         <v>45484</v>
       </c>
       <c r="H346" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="347" spans="1:8">
@@ -9373,13 +9394,13 @@
         <v>60060</v>
       </c>
       <c r="D347" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E347" s="2">
         <v>45498</v>
       </c>
       <c r="H347" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="348" spans="1:8">
@@ -9393,13 +9414,13 @@
         <v>67236</v>
       </c>
       <c r="D348" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E348" s="2">
         <v>45513</v>
       </c>
       <c r="H348" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="349" spans="1:8">
@@ -9413,13 +9434,13 @@
         <v>1413732</v>
       </c>
       <c r="D349" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E349" s="2">
         <v>45516</v>
       </c>
       <c r="H349" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="350" spans="1:8">
@@ -9433,13 +9454,13 @@
         <v>390516</v>
       </c>
       <c r="D350" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E350" s="2">
         <v>45516</v>
       </c>
       <c r="H350" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="351" spans="1:8">
@@ -9453,13 +9474,13 @@
         <v>350736</v>
       </c>
       <c r="D351" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E351" s="2">
         <v>45516</v>
       </c>
       <c r="H351" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="352" spans="1:8">
@@ -9473,13 +9494,13 @@
         <v>193860</v>
       </c>
       <c r="D352" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E352" s="2">
         <v>45526</v>
       </c>
       <c r="H352" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="353" spans="1:8">
@@ -9493,13 +9514,13 @@
         <v>49752</v>
       </c>
       <c r="D353" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E353" s="2">
         <v>45526</v>
       </c>
       <c r="H353" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="354" spans="1:8">
@@ -9513,13 +9534,13 @@
         <v>177066</v>
       </c>
       <c r="D354" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="E354" s="2">
         <v>45531</v>
       </c>
       <c r="H354" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -9533,16 +9554,16 @@
         <v>31956</v>
       </c>
       <c r="D355" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E355" s="2">
         <v>45534</v>
       </c>
       <c r="G355" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="H355" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="356" spans="1:8">
@@ -9556,13 +9577,13 @@
         <v>158161.92</v>
       </c>
       <c r="D356" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E356" s="2">
         <v>45545</v>
       </c>
       <c r="H356" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -9576,13 +9597,13 @@
         <v>53700</v>
       </c>
       <c r="D357" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E357" s="2">
         <v>45546</v>
       </c>
       <c r="H357" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="358" spans="1:8">
@@ -9596,13 +9617,13 @@
         <v>69000</v>
       </c>
       <c r="D358" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E358" s="2">
         <v>45551</v>
       </c>
       <c r="H358" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -9616,16 +9637,16 @@
         <v>24988</v>
       </c>
       <c r="D359" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E359" s="2">
         <v>45559</v>
       </c>
       <c r="G359" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H359" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="360" spans="1:8">
@@ -9639,13 +9660,150 @@
         <v>61860</v>
       </c>
       <c r="D360" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E360" s="2">
         <v>45561</v>
       </c>
       <c r="H360" t="s">
-        <v>426</v>
+        <v>432</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8">
+      <c r="A361" t="s">
+        <v>336</v>
+      </c>
+      <c r="B361">
+        <v>2024</v>
+      </c>
+      <c r="C361">
+        <v>63448.08</v>
+      </c>
+      <c r="D361" t="s">
+        <v>344</v>
+      </c>
+      <c r="E361" s="2">
+        <v>45574</v>
+      </c>
+      <c r="G361" t="s">
+        <v>405</v>
+      </c>
+      <c r="H361" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8">
+      <c r="A362" t="s">
+        <v>337</v>
+      </c>
+      <c r="B362">
+        <v>2024</v>
+      </c>
+      <c r="C362">
+        <v>76470</v>
+      </c>
+      <c r="D362" t="s">
+        <v>364</v>
+      </c>
+      <c r="E362" s="2">
+        <v>45565</v>
+      </c>
+      <c r="H362" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8">
+      <c r="A363" t="s">
+        <v>338</v>
+      </c>
+      <c r="B363">
+        <v>2024</v>
+      </c>
+      <c r="C363">
+        <v>264000</v>
+      </c>
+      <c r="D363" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8">
+      <c r="A364" t="s">
+        <v>339</v>
+      </c>
+      <c r="B364">
+        <v>2024</v>
+      </c>
+      <c r="C364">
+        <v>49680</v>
+      </c>
+      <c r="D364" t="s">
+        <v>367</v>
+      </c>
+      <c r="E364" s="2">
+        <v>45579</v>
+      </c>
+      <c r="H364" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8">
+      <c r="A365" t="s">
+        <v>339</v>
+      </c>
+      <c r="B365">
+        <v>2024</v>
+      </c>
+      <c r="C365">
+        <v>75936</v>
+      </c>
+      <c r="D365" t="s">
+        <v>350</v>
+      </c>
+      <c r="E365" s="2">
+        <v>45579</v>
+      </c>
+      <c r="H365" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8">
+      <c r="A366" t="s">
+        <v>340</v>
+      </c>
+      <c r="B366">
+        <v>2024</v>
+      </c>
+      <c r="C366">
+        <v>48204</v>
+      </c>
+      <c r="D366" t="s">
+        <v>346</v>
+      </c>
+      <c r="E366" s="2">
+        <v>45428</v>
+      </c>
+      <c r="H366" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8">
+      <c r="A367" t="s">
+        <v>341</v>
+      </c>
+      <c r="B367">
+        <v>2024</v>
+      </c>
+      <c r="C367">
+        <v>187944</v>
+      </c>
+      <c r="D367" t="s">
+        <v>349</v>
+      </c>
+      <c r="E367" s="2">
+        <v>45582</v>
+      </c>
+      <c r="H367" t="s">
+        <v>433</v>
       </c>
     </row>
   </sheetData>
